--- a/Old/Results_Original_Submission/Compare performance across thresholds.xlsx
+++ b/Old/Results_Original_Submission/Compare performance across thresholds.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -20,15 +20,6 @@
     <t xml:space="preserve">X25</t>
   </si>
   <si>
-    <t xml:space="preserve">X28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X32</t>
-  </si>
-  <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
@@ -47,55 +38,22 @@
     <t xml:space="preserve">62.0</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">specificity</t>
   </si>
   <si>
     <t xml:space="preserve">87.6</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">PPV</t>
   </si>
   <si>
     <t xml:space="preserve">14.5</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">NPV</t>
   </si>
   <si>
     <t xml:space="preserve">98.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3</t>
   </si>
   <si>
     <t xml:space="preserve">Events</t>
@@ -443,150 +401,69 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Old/Results_Original_Submission/Compare performance across thresholds.xlsx
+++ b/Old/Results_Original_Submission/Compare performance across thresholds.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -20,6 +20,15 @@
     <t xml:space="preserve">X25</t>
   </si>
   <si>
+    <t xml:space="preserve">X28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X32</t>
+  </si>
+  <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
@@ -38,22 +47,55 @@
     <t xml:space="preserve">62.0</t>
   </si>
   <si>
+    <t xml:space="preserve">58.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">specificity</t>
   </si>
   <si>
     <t xml:space="preserve">87.6</t>
   </si>
   <si>
+    <t xml:space="preserve">89.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPV</t>
   </si>
   <si>
     <t xml:space="preserve">14.5</t>
   </si>
   <si>
+    <t xml:space="preserve">15.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">NPV</t>
   </si>
   <si>
     <t xml:space="preserve">98.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3</t>
   </si>
   <si>
     <t xml:space="preserve">Events</t>
@@ -401,69 +443,150 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
